--- a/example_data/sample_7/elemen_3gr_boys.xlsx
+++ b/example_data/sample_7/elemen_3gr_boys.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20383"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\d\PYTHON\데이터\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DSMH\1_Class\4월28일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB094728-3D85-4204-9CB0-89F592B8CC26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7C1003-2D73-4F93-8742-DEA7C0A0BED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22830" windowHeight="9135" xr2:uid="{3B799A3D-E752-4EBB-93F4-E9C43126BECC}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="19386" windowHeight="11466" xr2:uid="{3B799A3D-E752-4EBB-93F4-E9C43126BECC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,11 +27,11 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>키</t>
+    <t>height</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>몸무게</t>
+    <t>weight</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -82,7 +82,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -398,9 +398,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24DAEBA6-DAD7-4461-BBBE-3ED0EF12040C}">
   <dimension ref="A1:B99"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.7" x14ac:dyDescent="0.65"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -408,7 +408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A2" s="1">
         <v>124.8</v>
       </c>
@@ -416,7 +416,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A3" s="1">
         <v>123.5</v>
       </c>
@@ -424,7 +424,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A4" s="1">
         <v>112.8</v>
       </c>
@@ -432,7 +432,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A5" s="1">
         <v>124.9</v>
       </c>
@@ -440,7 +440,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A6" s="1">
         <v>116.9</v>
       </c>
@@ -448,7 +448,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A7" s="1">
         <v>125.1</v>
       </c>
@@ -456,7 +456,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A8" s="1">
         <v>125.2</v>
       </c>
@@ -464,7 +464,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A9" s="1">
         <v>110.9</v>
       </c>
@@ -472,7 +472,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A10" s="1">
         <v>117.6</v>
       </c>
@@ -480,7 +480,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A11" s="1">
         <v>115.2</v>
       </c>
@@ -488,7 +488,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A12" s="1">
         <v>120.6</v>
       </c>
@@ -496,7 +496,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A13" s="1">
         <v>117.3</v>
       </c>
@@ -504,7 +504,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A14" s="1">
         <v>120.3</v>
       </c>
@@ -512,7 +512,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A15" s="1">
         <v>125</v>
       </c>
@@ -520,7 +520,7 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A16" s="1">
         <v>128.30000000000001</v>
       </c>
@@ -528,7 +528,7 @@
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A17" s="1">
         <v>120.8</v>
       </c>
@@ -536,7 +536,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A18" s="1">
         <v>132.30000000000001</v>
       </c>
@@ -544,7 +544,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A19" s="1">
         <v>133.6</v>
       </c>
@@ -552,7 +552,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A20" s="1">
         <v>115.3</v>
       </c>
@@ -560,7 +560,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A21" s="1">
         <v>127.2</v>
       </c>
@@ -568,7 +568,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A22" s="1">
         <v>129.6</v>
       </c>
@@ -576,7 +576,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A23" s="1">
         <v>120.7</v>
       </c>
@@ -584,7 +584,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A24" s="1">
         <v>126.8</v>
       </c>
@@ -592,7 +592,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A25" s="1">
         <v>130.80000000000001</v>
       </c>
@@ -600,7 +600,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A26" s="1">
         <v>126.2</v>
       </c>
@@ -608,7 +608,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A27" s="1">
         <v>110.9</v>
       </c>
@@ -616,7 +616,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A28" s="1">
         <v>131.6</v>
       </c>
@@ -624,7 +624,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A29" s="1">
         <v>127.1</v>
       </c>
@@ -632,7 +632,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A30" s="1">
         <v>129.1</v>
       </c>
@@ -640,7 +640,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A31" s="1">
         <v>131</v>
       </c>
@@ -648,7 +648,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A32" s="1">
         <v>128.80000000000001</v>
       </c>
@@ -656,7 +656,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A33" s="1">
         <v>131.6</v>
       </c>
@@ -664,7 +664,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A34" s="1">
         <v>144.6</v>
       </c>
@@ -672,7 +672,7 @@
         <v>46.6</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A35" s="1">
         <v>126</v>
       </c>
@@ -680,7 +680,7 @@
         <v>28.9</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A36" s="1">
         <v>134.1</v>
       </c>
@@ -688,7 +688,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A37" s="1">
         <v>119.3</v>
       </c>
@@ -696,7 +696,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A38" s="1">
         <v>147.4</v>
       </c>
@@ -704,7 +704,7 @@
         <v>46.1</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A39" s="1">
         <v>140.4</v>
       </c>
@@ -712,7 +712,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A40" s="1">
         <v>139.69999999999999</v>
       </c>
@@ -720,7 +720,7 @@
         <v>33.700000000000003</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A41" s="1">
         <v>132</v>
       </c>
@@ -728,7 +728,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A42" s="1">
         <v>126.9</v>
       </c>
@@ -736,7 +736,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A43" s="1">
         <v>142.1</v>
       </c>
@@ -744,7 +744,7 @@
         <v>32.4</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A44" s="1">
         <v>135.69999999999999</v>
       </c>
@@ -752,7 +752,7 @@
         <v>34.299999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A45" s="1">
         <v>137.19999999999999</v>
       </c>
@@ -760,7 +760,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A46" s="1">
         <v>140.30000000000001</v>
       </c>
@@ -768,7 +768,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A47" s="1">
         <v>142.1</v>
       </c>
@@ -776,7 +776,7 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A48" s="1">
         <v>139.1</v>
       </c>
@@ -784,7 +784,7 @@
         <v>32.1</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A49" s="1">
         <v>134.1</v>
       </c>
@@ -792,7 +792,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A50" s="1">
         <v>124</v>
       </c>
@@ -800,7 +800,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A51" s="1">
         <v>132.5</v>
       </c>
@@ -808,7 +808,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A52" s="1">
         <v>140.9</v>
       </c>
@@ -816,7 +816,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A53" s="1">
         <v>148.4</v>
       </c>
@@ -824,7 +824,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A54" s="1">
         <v>143.69999999999999</v>
       </c>
@@ -832,7 +832,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A55" s="1">
         <v>148.6</v>
       </c>
@@ -840,7 +840,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A56" s="1">
         <v>135.4</v>
       </c>
@@ -848,7 +848,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A57" s="1">
         <v>134.9</v>
       </c>
@@ -856,7 +856,7 @@
         <v>32.299999999999997</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A58" s="1">
         <v>157.4</v>
       </c>
@@ -864,7 +864,7 @@
         <v>56.7</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A59" s="1">
         <v>138.4</v>
       </c>
@@ -872,7 +872,7 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A60" s="1">
         <v>145.69999999999999</v>
       </c>
@@ -880,7 +880,7 @@
         <v>44.8</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A61" s="1">
         <v>138.5</v>
       </c>
@@ -888,7 +888,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A62" s="1">
         <v>148.6</v>
       </c>
@@ -896,7 +896,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A63" s="1">
         <v>134.30000000000001</v>
       </c>
@@ -904,7 +904,7 @@
         <v>33.200000000000003</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A64" s="1">
         <v>150.6</v>
       </c>
@@ -912,7 +912,7 @@
         <v>43.3</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A65" s="1">
         <v>140.30000000000001</v>
       </c>
@@ -920,7 +920,7 @@
         <v>34.1</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A66" s="1">
         <v>140.5</v>
       </c>
@@ -928,7 +928,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A67" s="1">
         <v>146.80000000000001</v>
       </c>
@@ -936,7 +936,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A68" s="1">
         <v>143.5</v>
       </c>
@@ -944,7 +944,7 @@
         <v>34.799999999999997</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A69" s="1">
         <v>163</v>
       </c>
@@ -952,7 +952,7 @@
         <v>53.6</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A70" s="1">
         <v>140.80000000000001</v>
       </c>
@@ -960,7 +960,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A71" s="1">
         <v>156.19999999999999</v>
       </c>
@@ -968,7 +968,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A72" s="1">
         <v>151.1</v>
       </c>
@@ -976,7 +976,7 @@
         <v>47.4</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A73" s="1">
         <v>150.69999999999999</v>
       </c>
@@ -984,7 +984,7 @@
         <v>40.9</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A74" s="1">
         <v>152.5</v>
       </c>
@@ -992,7 +992,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A75" s="1">
         <v>155</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A76" s="1">
         <v>147.19999999999999</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A77" s="1">
         <v>151</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>38.6</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A78" s="1">
         <v>153.4</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>51.3</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A79" s="1">
         <v>150.30000000000001</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A80" s="1">
         <v>124.1</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A81" s="1">
         <v>117.7</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A82" s="1">
         <v>118.6</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A83" s="1">
         <v>122</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A84" s="1">
         <v>124.8</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A85" s="1">
         <v>113.6</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A86" s="1">
         <v>114</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A87" s="1">
         <v>117</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A88" s="1">
         <v>132</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>41.7</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A89" s="1">
         <v>111.4</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A90" s="1">
         <v>116.8</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A91" s="1">
         <v>122.4</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A92" s="1">
         <v>130.9</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>30.5</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A93" s="1">
         <v>121.1</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A94" s="1">
         <v>122.8</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A95" s="1">
         <v>124</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A96" s="1">
         <v>115.9</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A97" s="1">
         <v>131.30000000000001</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A98" s="1">
         <v>128.9</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A99" s="1">
         <v>132.5</v>
       </c>
